--- a/Templates/Demo Data/MCDMStudio/MCDM_Demo_Data.xlsx
+++ b/Templates/Demo Data/MCDMStudio/MCDM_Demo_Data.xlsx
@@ -12,18 +12,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Criteria" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AHP Pairwise" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWARA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEMATEL Direct Relations" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISM SSIM" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANP Weighted Supermatrix" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FUCOM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DEMATEL Direct Relations" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ISM SSIM" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANP Weighted Supermatrix" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method Guide" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision Matrix'!$A$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Criteria'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AHP Pairwise'!$A$1:$E$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SWARA'!$A$1:$C$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'DEMATEL Direct Relations'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'ISM SSIM'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ANP Weighted Supermatrix'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'FUCOM'!$A$1:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DEMATEL Direct Relations'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ISM SSIM'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'ANP Weighted Supermatrix'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Method Guide'!$A$1:$C$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,15 +46,32 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00174C69"/>
+      <color rgb="0029465B"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00173B57"/>
       <sz val="15"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00173B57"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00718096"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,12 +80,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00174C69"/>
+        <fgColor rgb="00EAF1F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00173B57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2C6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8E1E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,13 +111,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -161,6 +209,176 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MCDMStudio</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Methods: All methods
+Purpose: Workbook layout, input rules and source notes.
+See the Method Guide sheet for the complete mapping.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MCDMStudio</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Methods: All methods
+Purpose: Quick lookup of which worksheets each method needs.
+See the Method Guide sheet for the complete mapping.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MCDMStudio</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Methods: SAW, TOPSIS, MOORA, MULTIMOORA, COPRAS-G, ARAS, WASPAS, VIKOR, ELECTRE I, PROMETHEE II, CoCoSo, EDAS, MARCOS, CODAS, MAIRCA, MABAC, GRA, PIV; Entropy, CRITIC, MEREC, Standard deviation, PSI weights
+Purpose: Alternative rows and criterion columns; also used by data-based objective weighting methods.
+See the Method Guide sheet for the complete mapping.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MCDMStudio</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Methods: All ranking methods; AHP, ANP, SWARA, BWM, FUCOM, Entropy, CRITIC, MEREC, Standard deviation, PSI weights; ISM
+Purpose: Criterion names; Benefit/Cost direction and manual weights for matrix methods; BWM comparisons where marked.
+See the Method Guide sheet for the complete mapping.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MCDMStudio</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Methods: AHP
+Purpose: Pairwise criterion comparisons.
+See the Method Guide sheet for the complete mapping.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MCDMStudio</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Methods: SWARA
+Purpose: Criterion priority order and relative importance values.
+See the Method Guide sheet for the complete mapping.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MCDMStudio</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Methods: FUCOM
+Purpose: Criterion order and comparative priorities between adjacent criteria.
+See the Method Guide sheet for the complete mapping.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MCDMStudio</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Methods: DEMATEL
+Purpose: Square factor-by-factor direct influence matrix (0–4; diagonal 0).
+See the Method Guide sheet for the complete mapping.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MCDMStudio</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Methods: ISM
+Purpose: Pairwise contextual relation judgments using V/A/X/O.
+See the Method Guide sheet for the complete mapping.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MCDMStudio</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Methods: ANP
+Purpose: Weighted, column-stochastic supermatrix.
+See the Method Guide sheet for the complete mapping.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -452,171 +670,308 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="105" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MCDMStudio numeric workbook</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Fill only yellow cells. Keep sheet names and headers unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+          <t>MCDMStudio | TOPSIS-style decision matrix</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Input cells are pale yellow. Rows are alternatives; columns are criteria/factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Enter alternatives, numeric criterion performances, direction, and optional weights.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Enter numeric performance values for each alternative and factor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Step 1 - Decision Matrix</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>One alternative per row; one numeric criterion per column. Avoid blank/negative cells unless method supports them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>One alternative per row; one numeric factor per column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Step 2 - Criteria</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>List criteria in the same order as Decision Matrix columns; choose Benefit or Cost.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Step 3 - Weights</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Weights include subjective AHP, ANP, SWARA, BWM and objective Entropy, CRITIC, MEREC, Standard deviation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Step 4 - AHP Pairwise</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Use Saaty 1–9 scale, reciprocal values (e.g. 3 and 1/3), diagonal = 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Step 5 - SWARA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Sort criteria from most to least important; set rank; s1=0; sⱼ is relative importance vs preceding criterion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Step 6 - BWM</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Mark one BWM best and one BWM worst criterion; enter each comparison vector on the 1–9 scale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Step 7 - DEMATEL Direct Relations</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Enter average expert influence on a 0–4 scale. Diagonal must be zero; nodes match criterion names.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Step 8 - ISM SSIM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Enter V/A/X/O in the upper triangle: i→j / j→i / both / none. Keep diagonal blank.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Step 9 - ANP Weighted Supermatrix</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Enter the already weighted, column-stochastic supermatrix (each column sums to 1); nodes match criteria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Outputs</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>In the app, choose a method and export all displayed calculations to Excel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MCDMStudio</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Educational numeric demonstration. Verify assumptions and judgment quality before research use.</t>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Use Benefit when higher is better and Cost when lower is better.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Step 3 - Weighting</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Choose weights in the app or enter manual weights in Criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Step 4 - Save</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Choose a method, edit any relevant sheet in the app, then save and calculate in one action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>TOPSIS: Thakkar (2021), Chapter 5. AHP: Chapter 3. See Method Guide and the app for sheet mappings and references.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Used by method(s)</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Purpose / expected data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Instructions</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>All methods</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Workbook layout, input rules and source notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Method Guide</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>All methods</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Quick lookup of which worksheets each method needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Decision Matrix</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>SAW, TOPSIS, MOORA, MULTIMOORA, COPRAS-G, ARAS, WASPAS, VIKOR, ELECTRE I, PROMETHEE II, CoCoSo, EDAS, MARCOS, CODAS, MAIRCA, MABAC, GRA, PIV; Entropy, CRITIC, MEREC, Standard deviation, PSI weights</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Alternative rows and criterion columns; also used by data-based objective weighting methods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Criteria</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>All ranking methods; AHP, ANP, SWARA, BWM, FUCOM, Entropy, CRITIC, MEREC, Standard deviation, PSI weights; ISM</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Criterion names; Benefit/Cost direction and manual weights for matrix methods; BWM comparisons where marked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>AHP Pairwise</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>AHP</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Pairwise criterion comparisons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>SWARA</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>SWARA</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Criterion priority order and relative importance values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>FUCOM</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>FUCOM</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Criterion order and comparative priorities between adjacent criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>ANP Weighted Supermatrix</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>ANP</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Weighted, column-stochastic supermatrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>DEMATEL Direct Relations</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>DEMATEL</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Square factor-by-factor direct influence matrix (0–4; diagonal 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>ISM SSIM</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>ISM</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Pairwise contextual relation judgments using V/A/X/O.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -636,112 +991,113 @@
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Alternative</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>C4</t>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>F4</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="6" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="6" t="n">
         <v>70</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="6" t="n">
         <v>85</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="6" t="n">
         <v>75</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -763,146 +1119,147 @@
     <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Manual weight</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>BWM best?</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>BWM worst?</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Best-to-criterion</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Criterion-to-worst</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Benefit</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="n">
+      <c r="E2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="6" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="6" t="n">
         <v>0.25</v>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr"/>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Benefit</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="6" t="n">
         <v>0.25</v>
       </c>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="n">
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="6" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Benefit</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="n">
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="6" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -922,112 +1279,113 @@
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>C4</t>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>F4</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="6" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="6" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>0.25</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="6" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1045,78 +1403,79 @@
     <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>s (relative importance)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>0.1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1126,122 +1485,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>C4</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Comparative priority to next</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1261,104 +1585,113 @@
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>C4</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>F4</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1378,111 +1711,230 @@
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.1</v>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.2</v>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr"/>
+      <c r="C3" s="6" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.3</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr"/>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>